--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,2283 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129751253</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>403198</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6826235</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129751333</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78833</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>403227</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6825952</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129751449</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>402790</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6827086</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129751513</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>403219</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6826206</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129751398</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>403238</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6826111</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129751396</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>403212</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6826253</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129751544</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>402836</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6827028</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129751593</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>403211</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6826017</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129751344</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>403202</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6825962</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129751597</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>402904</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6826932</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129751340</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>403229</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6826145</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129751376</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>402953</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6826856</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129751400</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>403247</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6826081</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129751292</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>403224</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6825996</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129751283</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>403210</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6826326</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129751284</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>403206</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6826289</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129751287</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>403213</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6826200</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129751447</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79665</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>402741</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6827113</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129751596</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>402957</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6826843</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129751522</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79170</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>967</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>402750</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6827121</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129751410</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>403193</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6825953</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129751263</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79694</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>403225</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6825954</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129751299</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>403210</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6826326</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>78833</v>
+        <v>78834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,54 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R11" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,64 +1663,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R12" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,72 +1769,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751340</v>
+        <v>129751376</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403229</v>
+        <v>402953</v>
       </c>
       <c r="R13" t="n">
-        <v>6826145</v>
+        <v>6826856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1867,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1895,45 +1885,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751376</v>
+        <v>129751340</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>8450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402953</v>
+        <v>403229</v>
       </c>
       <c r="R14" t="n">
-        <v>6826856</v>
+        <v>6826145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,6 +1973,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R15" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B16" t="n">
-        <v>79665</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R16" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79171</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R21" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79170</v>
+        <v>79076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R22" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B3" t="n">
-        <v>79695</v>
+        <v>78834</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R3" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B4" t="n">
-        <v>78834</v>
+        <v>79695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R4" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79666</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R15" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R16" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B24" t="n">
-        <v>79695</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,34 +2884,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R24" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>79695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,42 +2989,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R25" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>78834</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R3" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>79695</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R4" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B6" t="n">
-        <v>79666</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R6" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R7" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,45 +1584,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R11" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,72 +1672,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R12" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,19 +1770,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
         <v>129751376</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79171</v>
+        <v>79176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,42 +2884,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R24" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>79695</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,34 +2981,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R25" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R3" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R4" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1584,54 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R11" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,64 +1663,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R12" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,18 +1769,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B21" t="n">
-        <v>79176</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R21" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R22" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R3" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R4" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R6" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R7" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R21" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79176</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R22" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R3" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R4" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B6" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R6" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R7" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B21" t="n">
-        <v>79176</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R21" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R22" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,34 +2884,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R24" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,42 +2989,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R25" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R15" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B16" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R16" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79176</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R21" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79176</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R22" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R15" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R16" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>57896</v>
+        <v>79700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,42 +2884,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R24" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>79700</v>
+        <v>57896</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,34 +2981,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R25" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R3" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R4" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79671</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R15" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B16" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R16" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129751398</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>129751513</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129751597</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,45 +1788,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751376</v>
+        <v>129751340</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>8450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402953</v>
+        <v>403229</v>
       </c>
       <c r="R13" t="n">
-        <v>6826856</v>
+        <v>6826145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1876,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1885,54 +1895,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751340</v>
+        <v>129751376</v>
       </c>
       <c r="B14" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403229</v>
+        <v>402953</v>
       </c>
       <c r="R14" t="n">
-        <v>6826145</v>
+        <v>6826856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,7 +1974,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79671</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R15" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R16" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79176</v>
+        <v>79179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R3" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R4" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R6" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R7" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B21" t="n">
-        <v>79179</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R21" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R22" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R3" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R4" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B6" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R6" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R7" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B24" t="n">
-        <v>79703</v>
+        <v>57895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,34 +2884,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R24" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2970,10 +2978,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B25" t="n">
-        <v>57895</v>
+        <v>79703</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2981,42 +2989,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R25" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B3" t="n">
-        <v>79703</v>
+        <v>78845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R3" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R4" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R6" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R7" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>129751544</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,45 +1584,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R11" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,72 +1672,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R12" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,73 +1770,63 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751340</v>
+        <v>129751376</v>
       </c>
       <c r="B13" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403229</v>
+        <v>402953</v>
       </c>
       <c r="R13" t="n">
-        <v>6826145</v>
+        <v>6826856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1867,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1895,45 +1885,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751376</v>
+        <v>129751340</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402953</v>
+        <v>403229</v>
       </c>
       <c r="R14" t="n">
-        <v>6826856</v>
+        <v>6826145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,6 +1973,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129751596</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129751522</v>
       </c>
       <c r="B22" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129751299</v>
       </c>
       <c r="B24" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>129751263</v>
       </c>
       <c r="B25" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1788,45 +1788,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751376</v>
+        <v>129751340</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>402953</v>
+        <v>403229</v>
       </c>
       <c r="R13" t="n">
-        <v>6826856</v>
+        <v>6826145</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1876,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1885,54 +1895,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751340</v>
+        <v>129751376</v>
       </c>
       <c r="B14" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403229</v>
+        <v>402953</v>
       </c>
       <c r="R14" t="n">
-        <v>6826145</v>
+        <v>6826856</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1973,7 +1974,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R21" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79182</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R22" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2873,10 +2873,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751299</v>
+        <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>57898</v>
+        <v>79706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2884,42 +2884,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>403210</v>
+        <v>403225</v>
       </c>
       <c r="R24" t="n">
-        <v>6826326</v>
+        <v>6825954</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2978,10 +2970,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751263</v>
+        <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>57898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,34 +2981,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>403225</v>
+        <v>403210</v>
       </c>
       <c r="R25" t="n">
-        <v>6825954</v>
+        <v>6826326</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R15" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B16" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R16" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129751333</v>
+        <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,21 +809,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>403227</v>
+        <v>403198</v>
       </c>
       <c r="R3" t="n">
-        <v>6825952</v>
+        <v>6826235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129751253</v>
+        <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>403198</v>
+        <v>403227</v>
       </c>
       <c r="R4" t="n">
-        <v>6826235</v>
+        <v>6825952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B6" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R6" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R7" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,54 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R11" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,64 +1663,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R12" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,72 +1769,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751340</v>
+        <v>129751376</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403229</v>
+        <v>402953</v>
       </c>
       <c r="R13" t="n">
-        <v>6826145</v>
+        <v>6826856</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,7 +1867,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1895,45 +1885,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751376</v>
+        <v>129751340</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>402953</v>
+        <v>403229</v>
       </c>
       <c r="R14" t="n">
-        <v>6826856</v>
+        <v>6826145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1974,6 +1973,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751292</v>
+        <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403224</v>
+        <v>403247</v>
       </c>
       <c r="R15" t="n">
-        <v>6825996</v>
+        <v>6826081</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751400</v>
+        <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403247</v>
+        <v>403224</v>
       </c>
       <c r="R16" t="n">
-        <v>6826081</v>
+        <v>6825996</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79182</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1089,10 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129751398</v>
+        <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>403238</v>
+        <v>403219</v>
       </c>
       <c r="R6" t="n">
-        <v>6826111</v>
+        <v>6826206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,22 +1174,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751513</v>
+        <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,21 +1197,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>403219</v>
+        <v>403238</v>
       </c>
       <c r="R7" t="n">
-        <v>6826206</v>
+        <v>6826111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,12 +1271,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R21" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>79183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R22" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1584,45 +1584,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R11" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,72 +1672,64 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R12" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1769,19 +1770,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>129751253</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>129751333</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>129751449</v>
       </c>
       <c r="B5" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129751513</v>
       </c>
       <c r="B6" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>129751398</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>129751396</v>
       </c>
       <c r="B8" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129751593</v>
       </c>
       <c r="B10" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,54 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751344</v>
+        <v>129751597</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>403202</v>
+        <v>402904</v>
       </c>
       <c r="R11" t="n">
-        <v>6825962</v>
+        <v>6826932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,64 +1663,72 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751597</v>
+        <v>129751344</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>402904</v>
+        <v>403202</v>
       </c>
       <c r="R12" t="n">
-        <v>6826932</v>
+        <v>6825962</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,18 +1769,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1791,7 +1791,7 @@
         <v>129751376</v>
       </c>
       <c r="B13" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>129751400</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>129751292</v>
       </c>
       <c r="B16" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>129751283</v>
       </c>
       <c r="B17" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>129751284</v>
       </c>
       <c r="B18" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129751287</v>
       </c>
       <c r="B19" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>129751447</v>
       </c>
       <c r="B20" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751596</v>
+        <v>129751522</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2585,21 +2585,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2612,10 +2612,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>402957</v>
+        <v>402750</v>
       </c>
       <c r="R21" t="n">
-        <v>6826843</v>
+        <v>6827121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2675,10 +2675,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751522</v>
+        <v>129751596</v>
       </c>
       <c r="B22" t="n">
-        <v>79183</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,21 +2686,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>402750</v>
+        <v>402957</v>
       </c>
       <c r="R22" t="n">
-        <v>6827121</v>
+        <v>6826843</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2779,7 +2779,7 @@
         <v>129751410</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129751263</v>
       </c>
       <c r="B24" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>129751299</v>
       </c>
       <c r="B25" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AZ94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103320019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751522</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131515167</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103320588</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103319293</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751372</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751373</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1691,6 +1741,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751391</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1885,6 +1945,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751392</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1982,6 +2047,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751396</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2079,6 +2149,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751397</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751398</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2273,6 +2353,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751399</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2370,6 +2455,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751400</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751401</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2564,6 +2659,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751406</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2661,6 +2761,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751407</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2758,6 +2863,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751409</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2855,6 +2965,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751410</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2952,6 +3067,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751572</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3049,6 +3169,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751573</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3146,6 +3271,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751574</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3243,6 +3373,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751583</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3340,6 +3475,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751585</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3437,6 +3577,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751587</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3534,6 +3679,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751588</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3631,6 +3781,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751589</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3728,6 +3883,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751593</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3825,6 +3985,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751594</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3926,6 +4091,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751596</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4023,6 +4193,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751597</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4120,6 +4295,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036094</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4217,6 +4397,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751353</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4314,6 +4499,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751236</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4411,6 +4601,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751238</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4508,6 +4703,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751241</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4605,6 +4805,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751242</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4702,6 +4907,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751248</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4799,6 +5009,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751253</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4896,6 +5111,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751254</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4993,6 +5213,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751255</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5090,6 +5315,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751262</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5187,6 +5417,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751263</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5284,6 +5519,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751441</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5381,6 +5621,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751442</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5478,6 +5723,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751446</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5583,6 +5833,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751297</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5698,6 +5953,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133109711</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5816,6 +6076,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103320426</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5921,6 +6186,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751299</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6028,6 +6298,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751340</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6135,6 +6410,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751344</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6242,6 +6522,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751544</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6349,6 +6634,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751545</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6447,6 +6737,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103319162</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6545,6 +6840,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103320032</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6642,6 +6942,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751327</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6739,6 +7044,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751328</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6836,6 +7146,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751332</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6933,6 +7248,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751333</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7030,6 +7350,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751541</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7127,6 +7452,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751543</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7224,6 +7554,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751265</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7321,6 +7656,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751266</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7418,6 +7758,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751272</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7515,6 +7860,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751273</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7612,6 +7962,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751278</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7709,6 +8064,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751283</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7806,6 +8166,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751284</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7903,6 +8268,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751285</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8000,6 +8370,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751286</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8097,6 +8472,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751287</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8194,6 +8574,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751288</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8291,6 +8676,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751292</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8388,6 +8778,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751293</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8485,6 +8880,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751447</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8582,6 +8982,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751448</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8679,6 +9084,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751449</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8776,6 +9186,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751450</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8873,6 +9288,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751452</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8970,6 +9390,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751453</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9067,6 +9492,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751454</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9164,6 +9594,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751485</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9261,6 +9696,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751503</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9358,6 +9798,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751505</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9459,6 +9904,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751512</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9556,6 +10006,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751513</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9653,6 +10108,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751517</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9750,6 +10210,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751519</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9847,8 +10312,108 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751521</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ94"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1239,48 +1239,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129751372</v>
+        <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>93345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grundhån, Dlr</t>
+          <t>Buarhån , Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402836</v>
+        <v>403212</v>
       </c>
       <c r="R7" t="n">
-        <v>6827090</v>
+        <v>6826227</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,12 +1313,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,24 +1333,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751372</t>
+          <t>https://artportalen.se/Sighting/135863321</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129751373</v>
+        <v>129751372</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1376,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402840</v>
+        <v>402836</v>
       </c>
       <c r="R8" t="n">
-        <v>6827085</v>
+        <v>6827090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,13 +1446,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751373</t>
+          <t>https://artportalen.se/Sighting/129751372</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129751376</v>
+        <v>129751373</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1478,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402953</v>
+        <v>402840</v>
       </c>
       <c r="R9" t="n">
-        <v>6826856</v>
+        <v>6827085</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,13 +1548,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751376</t>
+          <t>https://artportalen.se/Sighting/129751373</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129751377</v>
+        <v>129751376</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1580,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402989</v>
+        <v>402953</v>
       </c>
       <c r="R10" t="n">
-        <v>6826849</v>
+        <v>6826856</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,13 +1650,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751377</t>
+          <t>https://artportalen.se/Sighting/129751376</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129751378</v>
+        <v>129751377</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1682,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402972</v>
+        <v>402989</v>
       </c>
       <c r="R11" t="n">
-        <v>6826850</v>
+        <v>6826849</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,13 +1752,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751378</t>
+          <t>https://artportalen.se/Sighting/129751377</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129751391</v>
+        <v>129751378</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1784,10 +1793,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>403159</v>
+        <v>402972</v>
       </c>
       <c r="R12" t="n">
-        <v>6826523</v>
+        <v>6826850</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,13 +1854,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751391</t>
+          <t>https://artportalen.se/Sighting/129751378</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129751392</v>
+        <v>129751391</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1886,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>403152</v>
+        <v>403159</v>
       </c>
       <c r="R13" t="n">
-        <v>6826521</v>
+        <v>6826523</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,13 +1956,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751392</t>
+          <t>https://artportalen.se/Sighting/129751391</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129751396</v>
+        <v>129751392</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1988,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>403212</v>
+        <v>403152</v>
       </c>
       <c r="R14" t="n">
-        <v>6826253</v>
+        <v>6826521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,13 +2058,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751396</t>
+          <t>https://artportalen.se/Sighting/129751392</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129751397</v>
+        <v>129751396</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2090,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>403216</v>
+        <v>403212</v>
       </c>
       <c r="R15" t="n">
-        <v>6826241</v>
+        <v>6826253</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,13 +2160,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751397</t>
+          <t>https://artportalen.se/Sighting/129751396</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129751398</v>
+        <v>129751397</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2192,10 +2201,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>403238</v>
+        <v>403216</v>
       </c>
       <c r="R16" t="n">
-        <v>6826111</v>
+        <v>6826241</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2253,13 +2262,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751398</t>
+          <t>https://artportalen.se/Sighting/129751397</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129751399</v>
+        <v>129751398</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2294,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>403256</v>
+        <v>403238</v>
       </c>
       <c r="R17" t="n">
-        <v>6826089</v>
+        <v>6826111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2355,13 +2364,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751399</t>
+          <t>https://artportalen.se/Sighting/129751398</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129751400</v>
+        <v>129751399</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2396,10 +2405,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>403247</v>
+        <v>403256</v>
       </c>
       <c r="R18" t="n">
-        <v>6826081</v>
+        <v>6826089</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,13 +2466,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751400</t>
+          <t>https://artportalen.se/Sighting/129751399</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129751401</v>
+        <v>129751400</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2498,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>403255</v>
+        <v>403247</v>
       </c>
       <c r="R19" t="n">
-        <v>6826065</v>
+        <v>6826081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2559,13 +2568,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751401</t>
+          <t>https://artportalen.se/Sighting/129751400</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129751406</v>
+        <v>129751401</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2600,10 +2609,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>403240</v>
+        <v>403255</v>
       </c>
       <c r="R20" t="n">
-        <v>6826002</v>
+        <v>6826065</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,13 +2670,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751406</t>
+          <t>https://artportalen.se/Sighting/129751401</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129751407</v>
+        <v>129751406</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2702,10 +2711,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>403220</v>
+        <v>403240</v>
       </c>
       <c r="R21" t="n">
-        <v>6825918</v>
+        <v>6826002</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,13 +2772,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751407</t>
+          <t>https://artportalen.se/Sighting/129751406</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129751409</v>
+        <v>129751407</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2804,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>403191</v>
+        <v>403220</v>
       </c>
       <c r="R22" t="n">
-        <v>6825953</v>
+        <v>6825918</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2865,13 +2874,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751409</t>
+          <t>https://artportalen.se/Sighting/129751407</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129751410</v>
+        <v>129751409</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2906,7 +2915,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>403193</v>
+        <v>403191</v>
       </c>
       <c r="R23" t="n">
         <v>6825953</v>
@@ -2967,13 +2976,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751410</t>
+          <t>https://artportalen.se/Sighting/129751409</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129751572</v>
+        <v>129751410</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -3008,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>402748</v>
+        <v>403193</v>
       </c>
       <c r="R24" t="n">
-        <v>6827151</v>
+        <v>6825953</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3058,24 +3067,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751572</t>
+          <t>https://artportalen.se/Sighting/129751410</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129751573</v>
+        <v>129751572</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3110,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>402746</v>
+        <v>402748</v>
       </c>
       <c r="R25" t="n">
-        <v>6827147</v>
+        <v>6827151</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3171,13 +3180,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751573</t>
+          <t>https://artportalen.se/Sighting/129751572</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129751574</v>
+        <v>129751573</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3212,10 +3221,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>402731</v>
+        <v>402746</v>
       </c>
       <c r="R26" t="n">
-        <v>6827144</v>
+        <v>6827147</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3273,13 +3282,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751574</t>
+          <t>https://artportalen.se/Sighting/129751573</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129751583</v>
+        <v>129751574</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3314,10 +3323,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>403174</v>
+        <v>402731</v>
       </c>
       <c r="R27" t="n">
-        <v>6826432</v>
+        <v>6827144</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,13 +3384,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751583</t>
+          <t>https://artportalen.se/Sighting/129751574</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129751585</v>
+        <v>129751583</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3416,10 +3425,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>403191</v>
+        <v>403174</v>
       </c>
       <c r="R28" t="n">
-        <v>6826033</v>
+        <v>6826432</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3477,13 +3486,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751585</t>
+          <t>https://artportalen.se/Sighting/129751583</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129751587</v>
+        <v>129751585</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3518,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>403257</v>
+        <v>403191</v>
       </c>
       <c r="R29" t="n">
-        <v>6826043</v>
+        <v>6826033</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3579,13 +3588,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751587</t>
+          <t>https://artportalen.se/Sighting/129751585</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129751588</v>
+        <v>129751587</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3620,7 +3629,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>403244</v>
+        <v>403257</v>
       </c>
       <c r="R30" t="n">
         <v>6826043</v>
@@ -3681,13 +3690,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751588</t>
+          <t>https://artportalen.se/Sighting/129751587</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129751589</v>
+        <v>129751588</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3722,10 +3731,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>403205</v>
+        <v>403244</v>
       </c>
       <c r="R31" t="n">
-        <v>6826004</v>
+        <v>6826043</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3783,13 +3792,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751589</t>
+          <t>https://artportalen.se/Sighting/129751588</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129751593</v>
+        <v>129751589</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3824,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>403211</v>
+        <v>403205</v>
       </c>
       <c r="R32" t="n">
-        <v>6826017</v>
+        <v>6826004</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3885,13 +3894,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751593</t>
+          <t>https://artportalen.se/Sighting/129751589</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129751594</v>
+        <v>129751593</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3926,10 +3935,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>403200</v>
+        <v>403211</v>
       </c>
       <c r="R33" t="n">
-        <v>6826010</v>
+        <v>6826017</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3987,13 +3996,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751594</t>
+          <t>https://artportalen.se/Sighting/129751593</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129751596</v>
+        <v>129751594</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -4022,19 +4031,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>402957</v>
+        <v>403200</v>
       </c>
       <c r="R34" t="n">
-        <v>6826843</v>
+        <v>6826010</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,7 +4081,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4093,13 +4098,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751596</t>
+          <t>https://artportalen.se/Sighting/129751594</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129751597</v>
+        <v>129751596</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4128,16 +4133,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>402904</v>
+        <v>402957</v>
       </c>
       <c r="R35" t="n">
-        <v>6826932</v>
+        <v>6826843</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4178,6 +4186,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4195,16 +4204,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751597</t>
+          <t>https://artportalen.se/Sighting/129751596</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133036094</v>
+        <v>129751597</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,14 +4241,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>403100</v>
+        <v>402904</v>
       </c>
       <c r="R36" t="n">
-        <v>6826569</v>
+        <v>6826932</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4266,12 +4275,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4297,51 +4306,51 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133036094</t>
+          <t>https://artportalen.se/Sighting/129751597</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129751353</v>
+        <v>133036094</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grundhån, Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>403227</v>
+        <v>403100</v>
       </c>
       <c r="R37" t="n">
-        <v>6825992</v>
+        <v>6826569</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4368,12 +4377,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4388,27 +4397,27 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751353</t>
+          <t>https://artportalen.se/Sighting/133036094</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129751236</v>
+        <v>129751353</v>
       </c>
       <c r="B38" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4416,21 +4425,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4440,10 +4449,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>402853</v>
+        <v>403227</v>
       </c>
       <c r="R38" t="n">
-        <v>6827057</v>
+        <v>6825992</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4501,13 +4510,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751236</t>
+          <t>https://artportalen.se/Sighting/129751353</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129751238</v>
+        <v>129751236</v>
       </c>
       <c r="B39" t="n">
         <v>79946</v>
@@ -4542,10 +4551,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>402874</v>
+        <v>402853</v>
       </c>
       <c r="R39" t="n">
-        <v>6827036</v>
+        <v>6827057</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4603,13 +4612,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751238</t>
+          <t>https://artportalen.se/Sighting/129751236</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129751241</v>
+        <v>129751238</v>
       </c>
       <c r="B40" t="n">
         <v>79946</v>
@@ -4644,10 +4653,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>402966</v>
+        <v>402874</v>
       </c>
       <c r="R40" t="n">
-        <v>6826794</v>
+        <v>6827036</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4705,13 +4714,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751241</t>
+          <t>https://artportalen.se/Sighting/129751238</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129751242</v>
+        <v>129751241</v>
       </c>
       <c r="B41" t="n">
         <v>79946</v>
@@ -4746,10 +4755,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>402974</v>
+        <v>402966</v>
       </c>
       <c r="R41" t="n">
-        <v>6826712</v>
+        <v>6826794</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4807,13 +4816,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751242</t>
+          <t>https://artportalen.se/Sighting/129751241</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129751248</v>
+        <v>129751242</v>
       </c>
       <c r="B42" t="n">
         <v>79946</v>
@@ -4848,10 +4857,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>403162</v>
+        <v>402974</v>
       </c>
       <c r="R42" t="n">
-        <v>6826500</v>
+        <v>6826712</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4909,13 +4918,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751248</t>
+          <t>https://artportalen.se/Sighting/129751242</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129751253</v>
+        <v>129751248</v>
       </c>
       <c r="B43" t="n">
         <v>79946</v>
@@ -4950,10 +4959,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>403198</v>
+        <v>403162</v>
       </c>
       <c r="R43" t="n">
-        <v>6826235</v>
+        <v>6826500</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5011,13 +5020,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751253</t>
+          <t>https://artportalen.se/Sighting/129751248</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129751254</v>
+        <v>129751253</v>
       </c>
       <c r="B44" t="n">
         <v>79946</v>
@@ -5052,10 +5061,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>403245</v>
+        <v>403198</v>
       </c>
       <c r="R44" t="n">
-        <v>6826141</v>
+        <v>6826235</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5113,13 +5122,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751254</t>
+          <t>https://artportalen.se/Sighting/129751253</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129751255</v>
+        <v>129751254</v>
       </c>
       <c r="B45" t="n">
         <v>79946</v>
@@ -5154,10 +5163,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>403206</v>
+        <v>403245</v>
       </c>
       <c r="R45" t="n">
-        <v>6826061</v>
+        <v>6826141</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5215,13 +5224,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751255</t>
+          <t>https://artportalen.se/Sighting/129751254</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129751262</v>
+        <v>129751255</v>
       </c>
       <c r="B46" t="n">
         <v>79946</v>
@@ -5256,10 +5265,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>403227</v>
+        <v>403206</v>
       </c>
       <c r="R46" t="n">
-        <v>6825992</v>
+        <v>6826061</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5317,13 +5326,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751262</t>
+          <t>https://artportalen.se/Sighting/129751255</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129751263</v>
+        <v>129751262</v>
       </c>
       <c r="B47" t="n">
         <v>79946</v>
@@ -5358,10 +5367,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>403225</v>
+        <v>403227</v>
       </c>
       <c r="R47" t="n">
-        <v>6825954</v>
+        <v>6825992</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5419,13 +5428,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751263</t>
+          <t>https://artportalen.se/Sighting/129751262</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129751441</v>
+        <v>129751263</v>
       </c>
       <c r="B48" t="n">
         <v>79946</v>
@@ -5460,10 +5469,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>403211</v>
+        <v>403225</v>
       </c>
       <c r="R48" t="n">
-        <v>6826160</v>
+        <v>6825954</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5510,24 +5519,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751441</t>
+          <t>https://artportalen.se/Sighting/129751263</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129751442</v>
+        <v>129751441</v>
       </c>
       <c r="B49" t="n">
         <v>79946</v>
@@ -5565,7 +5574,7 @@
         <v>403211</v>
       </c>
       <c r="R49" t="n">
-        <v>6826162</v>
+        <v>6826160</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5623,13 +5632,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751442</t>
+          <t>https://artportalen.se/Sighting/129751441</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129751446</v>
+        <v>129751442</v>
       </c>
       <c r="B50" t="n">
         <v>79946</v>
@@ -5664,10 +5673,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>403210</v>
+        <v>403211</v>
       </c>
       <c r="R50" t="n">
-        <v>6826044</v>
+        <v>6826162</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5725,59 +5734,51 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751446</t>
+          <t>https://artportalen.se/Sighting/129751442</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129751297</v>
+        <v>129751446</v>
       </c>
       <c r="B51" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>402844</v>
+        <v>403210</v>
       </c>
       <c r="R51" t="n">
-        <v>6827068</v>
+        <v>6826044</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5824,27 +5825,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751297</t>
+          <t>https://artportalen.se/Sighting/129751446</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133109711</v>
+        <v>129751297</v>
       </c>
       <c r="B52" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5880,14 +5881,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stor-Vargtjärn, Dlr</t>
+          <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>402975</v>
+        <v>402844</v>
       </c>
       <c r="R52" t="n">
-        <v>6826796</v>
+        <v>6827068</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5914,22 +5915,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5944,76 +5935,73 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133109711</t>
+          <t>https://artportalen.se/Sighting/129751297</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>103320426</v>
+        <v>133109711</v>
       </c>
       <c r="B53" t="n">
-        <v>58114</v>
+        <v>57162</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Grundhån , Dlr</t>
+          <t>Stor-Vargtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>402930</v>
+        <v>402975</v>
       </c>
       <c r="R53" t="n">
-        <v>6826886</v>
+        <v>6826796</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6037,22 +6025,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6067,24 +6055,24 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103320426</t>
+          <t>https://artportalen.se/Sighting/133109711</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129751299</v>
+        <v>103320426</v>
       </c>
       <c r="B54" t="n">
         <v>58114</v>
@@ -6112,28 +6100,31 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grundhån, Dlr</t>
+          <t>Grundhån , Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>403210</v>
+        <v>402930</v>
       </c>
       <c r="R54" t="n">
-        <v>6826326</v>
+        <v>6826886</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6157,12 +6148,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6177,58 +6178,57 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751299</t>
+          <t>https://artportalen.se/Sighting/103320426</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129751340</v>
+        <v>129751299</v>
       </c>
       <c r="B55" t="n">
-        <v>8455</v>
+        <v>58114</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -6238,10 +6238,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>403229</v>
+        <v>403210</v>
       </c>
       <c r="R55" t="n">
-        <v>6826145</v>
+        <v>6826326</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6282,7 +6282,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6300,13 +6299,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751340</t>
+          <t>https://artportalen.se/Sighting/129751299</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129751344</v>
+        <v>129751340</v>
       </c>
       <c r="B56" t="n">
         <v>8455</v>
@@ -6350,10 +6349,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>403202</v>
+        <v>403229</v>
       </c>
       <c r="R56" t="n">
-        <v>6825962</v>
+        <v>6826145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6412,13 +6411,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751344</t>
+          <t>https://artportalen.se/Sighting/129751340</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129751544</v>
+        <v>129751344</v>
       </c>
       <c r="B57" t="n">
         <v>8455</v>
@@ -6462,10 +6461,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>402836</v>
+        <v>403202</v>
       </c>
       <c r="R57" t="n">
-        <v>6827028</v>
+        <v>6825962</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6513,24 +6512,24 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751544</t>
+          <t>https://artportalen.se/Sighting/129751344</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129751545</v>
+        <v>129751544</v>
       </c>
       <c r="B58" t="n">
         <v>8455</v>
@@ -6574,10 +6573,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>403200</v>
+        <v>402836</v>
       </c>
       <c r="R58" t="n">
-        <v>6826154</v>
+        <v>6827028</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6636,55 +6635,63 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751545</t>
+          <t>https://artportalen.se/Sighting/129751544</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>103319162</v>
+        <v>129751545</v>
       </c>
       <c r="B59" t="n">
-        <v>79085</v>
+        <v>8455</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hörn , Dlr</t>
+          <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>403165</v>
+        <v>403200</v>
       </c>
       <c r="R59" t="n">
-        <v>6826462</v>
+        <v>6826154</v>
       </c>
       <c r="S59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6708,12 +6715,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6722,30 +6729,31 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103319162</t>
+          <t>https://artportalen.se/Sighting/129751545</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>103320032</v>
+        <v>103319162</v>
       </c>
       <c r="B60" t="n">
         <v>79085</v>
@@ -6777,14 +6785,14 @@
       <c r="K60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Buarhån , Dlr</t>
+          <t>Hörn , Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>403214</v>
+        <v>403165</v>
       </c>
       <c r="R60" t="n">
-        <v>6826041</v>
+        <v>6826462</v>
       </c>
       <c r="S60" t="n">
         <v>2</v>
@@ -6842,13 +6850,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103320032</t>
+          <t>https://artportalen.se/Sighting/103319162</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129751327</v>
+        <v>103320032</v>
       </c>
       <c r="B61" t="n">
         <v>79085</v>
@@ -6877,19 +6885,20 @@
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Grundhån, Dlr</t>
+          <t>Buarhån , Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>403162</v>
+        <v>403214</v>
       </c>
       <c r="R61" t="n">
-        <v>6826500</v>
+        <v>6826041</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6913,12 +6922,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6933,24 +6942,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751327</t>
+          <t>https://artportalen.se/Sighting/103320032</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129751328</v>
+        <v>129751327</v>
       </c>
       <c r="B62" t="n">
         <v>79085</v>
@@ -6985,10 +6994,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>403177</v>
+        <v>403162</v>
       </c>
       <c r="R62" t="n">
-        <v>6826476</v>
+        <v>6826500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7046,13 +7055,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751328</t>
+          <t>https://artportalen.se/Sighting/129751327</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129751332</v>
+        <v>129751328</v>
       </c>
       <c r="B63" t="n">
         <v>79085</v>
@@ -7087,10 +7096,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>403227</v>
+        <v>403177</v>
       </c>
       <c r="R63" t="n">
-        <v>6825992</v>
+        <v>6826476</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7148,13 +7157,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751332</t>
+          <t>https://artportalen.se/Sighting/129751328</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129751333</v>
+        <v>129751332</v>
       </c>
       <c r="B64" t="n">
         <v>79085</v>
@@ -7192,7 +7201,7 @@
         <v>403227</v>
       </c>
       <c r="R64" t="n">
-        <v>6825952</v>
+        <v>6825992</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7250,13 +7259,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751333</t>
+          <t>https://artportalen.se/Sighting/129751332</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129751541</v>
+        <v>129751333</v>
       </c>
       <c r="B65" t="n">
         <v>79085</v>
@@ -7291,10 +7300,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>403264</v>
+        <v>403227</v>
       </c>
       <c r="R65" t="n">
-        <v>6826059</v>
+        <v>6825952</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,24 +7350,24 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751541</t>
+          <t>https://artportalen.se/Sighting/129751333</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129751543</v>
+        <v>129751541</v>
       </c>
       <c r="B66" t="n">
         <v>79085</v>
@@ -7393,10 +7402,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>403210</v>
+        <v>403264</v>
       </c>
       <c r="R66" t="n">
-        <v>6826044</v>
+        <v>6826059</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7454,16 +7463,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751543</t>
+          <t>https://artportalen.se/Sighting/129751541</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129751265</v>
+        <v>129751543</v>
       </c>
       <c r="B67" t="n">
-        <v>79917</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7471,21 +7480,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7495,10 +7504,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>402846</v>
+        <v>403210</v>
       </c>
       <c r="R67" t="n">
-        <v>6827056</v>
+        <v>6826044</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7545,24 +7554,24 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Louise Tegnér</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751265</t>
+          <t>https://artportalen.se/Sighting/129751543</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129751266</v>
+        <v>129751265</v>
       </c>
       <c r="B68" t="n">
         <v>79917</v>
@@ -7597,10 +7606,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>402873</v>
+        <v>402846</v>
       </c>
       <c r="R68" t="n">
-        <v>6827037</v>
+        <v>6827056</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7658,13 +7667,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751266</t>
+          <t>https://artportalen.se/Sighting/129751265</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129751272</v>
+        <v>129751266</v>
       </c>
       <c r="B69" t="n">
         <v>79917</v>
@@ -7699,10 +7708,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>402969</v>
+        <v>402873</v>
       </c>
       <c r="R69" t="n">
-        <v>6826687</v>
+        <v>6827037</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7760,13 +7769,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751272</t>
+          <t>https://artportalen.se/Sighting/129751266</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129751273</v>
+        <v>129751272</v>
       </c>
       <c r="B70" t="n">
         <v>79917</v>
@@ -7801,10 +7810,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>402975</v>
+        <v>402969</v>
       </c>
       <c r="R70" t="n">
-        <v>6826707</v>
+        <v>6826687</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7862,13 +7871,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751273</t>
+          <t>https://artportalen.se/Sighting/129751272</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129751278</v>
+        <v>129751273</v>
       </c>
       <c r="B71" t="n">
         <v>79917</v>
@@ -7903,10 +7912,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>403162</v>
+        <v>402975</v>
       </c>
       <c r="R71" t="n">
-        <v>6826499</v>
+        <v>6826707</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7964,13 +7973,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751278</t>
+          <t>https://artportalen.se/Sighting/129751273</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129751283</v>
+        <v>129751278</v>
       </c>
       <c r="B72" t="n">
         <v>79917</v>
@@ -8005,10 +8014,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>403210</v>
+        <v>403162</v>
       </c>
       <c r="R72" t="n">
-        <v>6826326</v>
+        <v>6826499</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8066,13 +8075,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751283</t>
+          <t>https://artportalen.se/Sighting/129751278</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129751284</v>
+        <v>129751283</v>
       </c>
       <c r="B73" t="n">
         <v>79917</v>
@@ -8107,10 +8116,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>403206</v>
+        <v>403210</v>
       </c>
       <c r="R73" t="n">
-        <v>6826289</v>
+        <v>6826326</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8168,13 +8177,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751284</t>
+          <t>https://artportalen.se/Sighting/129751283</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129751285</v>
+        <v>129751284</v>
       </c>
       <c r="B74" t="n">
         <v>79917</v>
@@ -8209,10 +8218,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>403226</v>
+        <v>403206</v>
       </c>
       <c r="R74" t="n">
-        <v>6826262</v>
+        <v>6826289</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8270,13 +8279,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751285</t>
+          <t>https://artportalen.se/Sighting/129751284</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129751286</v>
+        <v>129751285</v>
       </c>
       <c r="B75" t="n">
         <v>79917</v>
@@ -8311,10 +8320,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>403214</v>
+        <v>403226</v>
       </c>
       <c r="R75" t="n">
-        <v>6826244</v>
+        <v>6826262</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8372,13 +8381,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751286</t>
+          <t>https://artportalen.se/Sighting/129751285</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129751287</v>
+        <v>129751286</v>
       </c>
       <c r="B76" t="n">
         <v>79917</v>
@@ -8413,10 +8422,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>403213</v>
+        <v>403214</v>
       </c>
       <c r="R76" t="n">
-        <v>6826200</v>
+        <v>6826244</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8474,13 +8483,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751287</t>
+          <t>https://artportalen.se/Sighting/129751286</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129751288</v>
+        <v>129751287</v>
       </c>
       <c r="B77" t="n">
         <v>79917</v>
@@ -8515,10 +8524,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>403207</v>
+        <v>403213</v>
       </c>
       <c r="R77" t="n">
-        <v>6826061</v>
+        <v>6826200</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8576,13 +8585,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751288</t>
+          <t>https://artportalen.se/Sighting/129751287</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129751292</v>
+        <v>129751288</v>
       </c>
       <c r="B78" t="n">
         <v>79917</v>
@@ -8617,10 +8626,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>403224</v>
+        <v>403207</v>
       </c>
       <c r="R78" t="n">
-        <v>6825996</v>
+        <v>6826061</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8678,13 +8687,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751292</t>
+          <t>https://artportalen.se/Sighting/129751288</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129751293</v>
+        <v>129751292</v>
       </c>
       <c r="B79" t="n">
         <v>79917</v>
@@ -8719,10 +8728,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>403233</v>
+        <v>403224</v>
       </c>
       <c r="R79" t="n">
-        <v>6825958</v>
+        <v>6825996</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8780,13 +8789,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751293</t>
+          <t>https://artportalen.se/Sighting/129751292</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129751447</v>
+        <v>129751293</v>
       </c>
       <c r="B80" t="n">
         <v>79917</v>
@@ -8821,10 +8830,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>402741</v>
+        <v>403233</v>
       </c>
       <c r="R80" t="n">
-        <v>6827113</v>
+        <v>6825958</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8871,24 +8880,24 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Louise Tegnér</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751447</t>
+          <t>https://artportalen.se/Sighting/129751293</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129751448</v>
+        <v>129751447</v>
       </c>
       <c r="B81" t="n">
         <v>79917</v>
@@ -8923,10 +8932,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>402749</v>
+        <v>402741</v>
       </c>
       <c r="R81" t="n">
-        <v>6827079</v>
+        <v>6827113</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8984,13 +8993,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751448</t>
+          <t>https://artportalen.se/Sighting/129751447</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129751449</v>
+        <v>129751448</v>
       </c>
       <c r="B82" t="n">
         <v>79917</v>
@@ -9025,10 +9034,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>402790</v>
+        <v>402749</v>
       </c>
       <c r="R82" t="n">
-        <v>6827086</v>
+        <v>6827079</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9086,13 +9095,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751449</t>
+          <t>https://artportalen.se/Sighting/129751448</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129751450</v>
+        <v>129751449</v>
       </c>
       <c r="B83" t="n">
         <v>79917</v>
@@ -9127,10 +9136,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>402792</v>
+        <v>402790</v>
       </c>
       <c r="R83" t="n">
-        <v>6827045</v>
+        <v>6827086</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9188,13 +9197,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751450</t>
+          <t>https://artportalen.se/Sighting/129751449</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129751452</v>
+        <v>129751450</v>
       </c>
       <c r="B84" t="n">
         <v>79917</v>
@@ -9229,10 +9238,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>402803</v>
+        <v>402792</v>
       </c>
       <c r="R84" t="n">
-        <v>6827030</v>
+        <v>6827045</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9290,13 +9299,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751452</t>
+          <t>https://artportalen.se/Sighting/129751450</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129751453</v>
+        <v>129751452</v>
       </c>
       <c r="B85" t="n">
         <v>79917</v>
@@ -9331,10 +9340,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>402828</v>
+        <v>402803</v>
       </c>
       <c r="R85" t="n">
-        <v>6827005</v>
+        <v>6827030</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9392,13 +9401,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751453</t>
+          <t>https://artportalen.se/Sighting/129751452</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129751454</v>
+        <v>129751453</v>
       </c>
       <c r="B86" t="n">
         <v>79917</v>
@@ -9433,10 +9442,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>402857</v>
+        <v>402828</v>
       </c>
       <c r="R86" t="n">
-        <v>6826980</v>
+        <v>6827005</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9494,13 +9503,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751454</t>
+          <t>https://artportalen.se/Sighting/129751453</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129751485</v>
+        <v>129751454</v>
       </c>
       <c r="B87" t="n">
         <v>79917</v>
@@ -9535,10 +9544,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>402994</v>
+        <v>402857</v>
       </c>
       <c r="R87" t="n">
-        <v>6826609</v>
+        <v>6826980</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9596,13 +9605,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751485</t>
+          <t>https://artportalen.se/Sighting/129751454</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129751503</v>
+        <v>129751485</v>
       </c>
       <c r="B88" t="n">
         <v>79917</v>
@@ -9637,10 +9646,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>403122</v>
+        <v>402994</v>
       </c>
       <c r="R88" t="n">
-        <v>6826449</v>
+        <v>6826609</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9698,13 +9707,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751503</t>
+          <t>https://artportalen.se/Sighting/129751485</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129751505</v>
+        <v>129751503</v>
       </c>
       <c r="B89" t="n">
         <v>79917</v>
@@ -9739,10 +9748,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>403174</v>
+        <v>403122</v>
       </c>
       <c r="R89" t="n">
-        <v>6826435</v>
+        <v>6826449</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9800,13 +9809,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751505</t>
+          <t>https://artportalen.se/Sighting/129751503</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129751512</v>
+        <v>129751505</v>
       </c>
       <c r="B90" t="n">
         <v>79917</v>
@@ -9835,19 +9844,16 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>403175</v>
+        <v>403174</v>
       </c>
       <c r="R90" t="n">
-        <v>6826234</v>
+        <v>6826435</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9888,7 +9894,6 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9906,13 +9911,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751512</t>
+          <t>https://artportalen.se/Sighting/129751505</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129751513</v>
+        <v>129751512</v>
       </c>
       <c r="B91" t="n">
         <v>79917</v>
@@ -9941,16 +9946,19 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Grundhån, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>403219</v>
+        <v>403175</v>
       </c>
       <c r="R91" t="n">
-        <v>6826206</v>
+        <v>6826234</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9991,6 +9999,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -10008,13 +10017,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751513</t>
+          <t>https://artportalen.se/Sighting/129751512</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129751517</v>
+        <v>129751513</v>
       </c>
       <c r="B92" t="n">
         <v>79917</v>
@@ -10049,10 +10058,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>403211</v>
+        <v>403219</v>
       </c>
       <c r="R92" t="n">
-        <v>6826160</v>
+        <v>6826206</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10110,13 +10119,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751517</t>
+          <t>https://artportalen.se/Sighting/129751513</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129751519</v>
+        <v>129751517</v>
       </c>
       <c r="B93" t="n">
         <v>79917</v>
@@ -10151,10 +10160,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>403266</v>
+        <v>403211</v>
       </c>
       <c r="R93" t="n">
-        <v>6826053</v>
+        <v>6826160</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10212,13 +10221,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129751519</t>
+          <t>https://artportalen.se/Sighting/129751517</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129751521</v>
+        <v>129751519</v>
       </c>
       <c r="B94" t="n">
         <v>79917</v>
@@ -10253,10 +10262,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>403196</v>
+        <v>403266</v>
       </c>
       <c r="R94" t="n">
-        <v>6826154</v>
+        <v>6826053</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10313,6 +10322,108 @@
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129751519</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129751521</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Grundhån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>403196</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6826154</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Särna</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129751521</t>
         </is>
@@ -10413,6 +10524,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 14277-2024 artfynd.xlsx
+++ b/artfynd/A 14277-2024 artfynd.xlsx
@@ -1242,7 +1242,7 @@
         <v>135863321</v>
       </c>
       <c r="B7" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
